--- a/Dataset/IT/xlsx/ITAMed_2024.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2024.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Chirurgia Generale</t>
+          <t>Chirurgia Generale; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Nefrologia; Ematologia</t>
+          <t>Ematologia; Nefrologia</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Ematologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Pediatria</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Oncologia; Urologia</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>Oncologia; Farmacologia e Tossicologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Oftalmologia; Pediatria</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Genetica Medica; Endocrinologia</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Pediatria</t>
+          <t>Pediatria; Gastroenterologia</t>
         </is>
       </c>
       <c r="L96" s="5" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Pediatria</t>
+          <t>Pediatria; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Ortopedia e Traumatologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Oncologia</t>
+          <t>Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>Oncologia; Dermatologia e Venereologia</t>
+          <t>Dermatologia e Venereologia; Oncologia</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Ortopedia e Traumatologia</t>
+          <t>Ortopedia e Traumatologia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>Ematologia; Gastroenterologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2024.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2024.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M2" s="5" t="n"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M3" s="5" t="n"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M4" s="5" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M5" s="5" t="n"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M7" s="5" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M8" s="5" t="n"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M9" s="5" t="n"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M10" s="5" t="n"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M11" s="5" t="n"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M13" s="5" t="n"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M15" s="5" t="n"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M16" s="5" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M17" s="5" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M18" s="5" t="n"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M19" s="5" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M20" s="5" t="n"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M21" s="5" t="n"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M22" s="5" t="n"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M23" s="5" t="n"/>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M24" s="5" t="n"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M25" s="5" t="n"/>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M26" s="5" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M28" s="5" t="n"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M29" s="5" t="n"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M30" s="5" t="n"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M31" s="5" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M32" s="5" t="n"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M33" s="5" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M34" s="5" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M35" s="5" t="n"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M36" s="5" t="n"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M37" s="5" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M38" s="5" t="n"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M39" s="5" t="n"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M40" s="5" t="n"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M41" s="5" t="n"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M42" s="5" t="n"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M45" s="5" t="n"/>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M46" s="5" t="n"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M47" s="5" t="n"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M48" s="5" t="n"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M49" s="5" t="n"/>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M50" s="5" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M51" s="5" t="n"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M52" s="5" t="n"/>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M53" s="5" t="n"/>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M54" s="5" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M55" s="5" t="n"/>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M56" s="5" t="n"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M57" s="5" t="n"/>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M58" s="5" t="n"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M59" s="5" t="n"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M60" s="5" t="n"/>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" s="5" t="n"/>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M62" s="5" t="n"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M63" s="5" t="n"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M64" s="5" t="n"/>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M66" s="5" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M67" s="5" t="n"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M68" s="5" t="n"/>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M69" s="5" t="n"/>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M70" s="5" t="n"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M71" s="5" t="n"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M72" s="5" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M73" s="5" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M75" s="5" t="n"/>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M76" s="5" t="n"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M77" s="5" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M78" s="5" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M79" s="5" t="n"/>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M80" s="5" t="n"/>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M81" s="5" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M82" s="5" t="n"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M83" s="5" t="n"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M84" s="5" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M85" s="5" t="n"/>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M86" s="5" t="n"/>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M87" s="5" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M88" s="5" t="n"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M89" s="5" t="n"/>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M90" s="5" t="n"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M91" s="5" t="n"/>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M92" s="5" t="n"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M93" s="5" t="n"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M94" s="5" t="n"/>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M95" s="5" t="n"/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" s="5" t="n"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M97" s="5" t="n"/>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M98" s="5" t="n"/>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M99" s="5" t="n"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M100" s="5" t="n"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M101" s="5" t="n"/>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M102" s="5" t="n"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M103" s="5" t="n"/>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M104" s="5" t="n"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M105" s="5" t="n"/>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M106" s="5" t="n"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M107" s="5" t="n"/>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M108" s="5" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M109" s="5" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M110" s="5" t="n"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" s="5" t="n"/>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M112" s="5" t="n"/>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M113" s="5" t="n"/>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M114" s="5" t="n"/>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M115" s="5" t="n"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M116" s="5" t="n"/>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M117" s="5" t="n"/>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M118" s="5" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M119" s="5" t="n"/>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M120" s="5" t="n"/>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M122" s="5" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M123" s="5" t="n"/>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M124" s="5" t="n"/>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M125" s="5" t="n"/>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M126" s="5" t="n"/>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M127" s="5" t="n"/>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M128" s="5" t="n"/>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M129" s="5" t="n"/>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M130" s="5" t="n"/>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M131" s="5" t="n"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M132" s="5" t="n"/>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M133" s="5" t="n"/>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M136" s="5" t="n"/>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M137" s="5" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M138" s="5" t="n"/>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M140" s="5" t="n"/>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M141" s="5" t="n"/>

--- a/Dataset/IT/xlsx/ITAMed_2024.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2024.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -517,15 +517,20 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
+          <t>Tipo Domanda</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -588,8 +593,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -648,8 +658,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -708,8 +723,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M4" s="5" t="n"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -768,8 +788,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M5" s="5" t="n"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -828,8 +853,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M6" s="5" t="n"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -888,8 +918,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M7" s="5" t="n"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -948,8 +983,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M8" s="5" t="n"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1008,8 +1048,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M9" s="5" t="n"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -1068,8 +1113,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M10" s="5" t="n"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1128,8 +1178,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M11" s="5" t="n"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1188,8 +1243,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M12" s="5" t="n"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1248,8 +1308,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M13" s="5" t="n"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1308,8 +1373,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M14" s="5" t="n"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1368,8 +1438,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M15" s="5" t="n"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1428,8 +1503,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M16" s="5" t="n"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1488,8 +1568,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M17" s="5" t="n"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1548,8 +1633,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M18" s="5" t="n"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1608,8 +1698,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M19" s="5" t="n"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1668,8 +1763,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M20" s="5" t="n"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1728,8 +1828,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M21" s="5" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -1788,8 +1893,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M22" s="5" t="n"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1848,8 +1958,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M23" s="5" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -1908,8 +2023,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M24" s="5" t="n"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1968,8 +2088,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M25" s="5" t="n"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -2028,8 +2153,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M26" s="5" t="n"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -2088,8 +2218,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M27" s="5" t="n"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -2148,8 +2283,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M28" s="5" t="n"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -2208,8 +2348,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M29" s="5" t="n"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -2268,8 +2413,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M30" s="5" t="n"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -2328,8 +2478,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M31" s="5" t="n"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -2388,8 +2543,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M32" s="5" t="n"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -2448,8 +2608,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M33" s="5" t="n"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -2508,8 +2673,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M34" s="5" t="n"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -2568,8 +2738,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M35" s="5" t="n"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -2628,8 +2803,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M36" s="5" t="n"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -2688,8 +2868,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M37" s="5" t="n"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -2748,8 +2933,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M38" s="5" t="n"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -2808,8 +2998,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M39" s="5" t="n"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -2868,8 +3063,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M40" s="5" t="n"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -2928,8 +3128,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M41" s="5" t="n"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -2988,8 +3193,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M42" s="5" t="n"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -3048,12 +3258,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023622.png</t>
         </is>
@@ -3116,12 +3331,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023623.png</t>
         </is>
@@ -3184,8 +3404,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M45" s="5" t="n"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -3244,8 +3469,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M46" s="5" t="n"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -3304,8 +3534,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M47" s="5" t="n"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -3364,8 +3599,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M48" s="5" t="n"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -3424,8 +3664,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M49" s="5" t="n"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -3484,8 +3729,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M50" s="5" t="n"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -3544,8 +3794,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M51" s="5" t="n"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -3604,8 +3859,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M52" s="5" t="n"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -3664,8 +3924,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M53" s="5" t="n"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -3724,8 +3989,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M54" s="5" t="n"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -3784,8 +4054,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M55" s="5" t="n"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -3844,8 +4119,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M56" s="5" t="n"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -3904,8 +4184,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M57" s="5" t="n"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -3964,8 +4249,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M58" s="5" t="n"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -4024,8 +4314,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M59" s="5" t="n"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -4084,8 +4379,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M60" s="5" t="n"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -4144,8 +4444,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M61" s="5" t="n"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -4204,8 +4509,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M62" s="5" t="n"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -4264,8 +4574,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M63" s="5" t="n"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -4324,8 +4639,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M64" s="5" t="n"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -4384,12 +4704,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>Spirometry report</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023644.png</t>
         </is>
@@ -4452,8 +4777,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M66" s="5" t="n"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -4512,8 +4842,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M67" s="5" t="n"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -4572,8 +4907,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M68" s="5" t="n"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -4632,8 +4972,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M69" s="5" t="n"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -4692,8 +5037,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M70" s="5" t="n"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -4752,8 +5102,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M71" s="5" t="n"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -4812,8 +5167,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M72" s="5" t="n"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -4872,8 +5232,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M73" s="5" t="n"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -4932,12 +5297,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023653.png</t>
         </is>
@@ -5000,8 +5370,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M75" s="5" t="n"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N75" s="5" t="n"/>
+      <c r="O75" s="5" t="n"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" s="3" t="n">
@@ -5060,8 +5435,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -5120,8 +5500,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M77" s="5" t="n"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" s="3" t="n">
@@ -5180,8 +5565,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M78" s="5" t="n"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -5240,8 +5630,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M79" s="5" t="n"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -5300,8 +5695,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M80" s="5" t="n"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -5360,8 +5760,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M81" s="5" t="n"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -5420,8 +5825,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M82" s="5" t="n"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -5480,8 +5890,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M83" s="5" t="n"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -5540,8 +5955,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M84" s="5" t="n"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -5600,8 +6020,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M85" s="5" t="n"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -5660,8 +6085,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M86" s="5" t="n"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -5720,8 +6150,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M87" s="5" t="n"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -5780,8 +6215,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M88" s="5" t="n"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -5840,8 +6280,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M89" s="5" t="n"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -5900,8 +6345,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M90" s="5" t="n"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -5960,8 +6410,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M91" s="5" t="n"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -6020,8 +6475,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M92" s="5" t="n"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -6080,8 +6540,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M93" s="5" t="n"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -6140,8 +6605,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M94" s="5" t="n"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -6200,8 +6670,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M95" s="5" t="n"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -6260,8 +6735,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M96" s="5" t="n"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -6320,8 +6800,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M97" s="5" t="n"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -6380,8 +6865,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M98" s="5" t="n"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -6440,8 +6930,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M99" s="5" t="n"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N99" s="5" t="n"/>
+      <c r="O99" s="5" t="n"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -6500,8 +6995,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M100" s="5" t="n"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
     </row>
     <row r="101" ht="18.75" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -6560,8 +7060,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M101" s="5" t="n"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
     </row>
     <row r="102" ht="18.75" customHeight="1">
       <c r="A102" s="3" t="n">
@@ -6620,8 +7125,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M102" s="5" t="n"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
     </row>
     <row r="103" ht="18.75" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -6680,8 +7190,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M103" s="5" t="n"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
     </row>
     <row r="104" ht="18.75" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -6740,8 +7255,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M104" s="5" t="n"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
     </row>
     <row r="105" ht="18.75" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -6800,8 +7320,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M105" s="5" t="n"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
     </row>
     <row r="106" ht="18.75" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -6860,8 +7385,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M106" s="5" t="n"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
     </row>
     <row r="107" ht="18.75" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -6920,8 +7450,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M107" s="5" t="n"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
     </row>
     <row r="108" ht="18.75" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -6980,8 +7515,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M108" s="5" t="n"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -7040,8 +7580,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M109" s="5" t="n"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -7100,8 +7645,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M110" s="5" t="n"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -7160,8 +7710,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M111" s="5" t="n"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -7220,8 +7775,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M112" s="5" t="n"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
     </row>
     <row r="113" ht="18.75" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -7280,8 +7840,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M113" s="5" t="n"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -7340,8 +7905,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M114" s="5" t="n"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -7400,8 +7970,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M115" s="5" t="n"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -7460,8 +8035,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M116" s="5" t="n"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N116" s="5" t="n"/>
+      <c r="O116" s="5" t="n"/>
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -7520,8 +8100,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M117" s="5" t="n"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -7580,8 +8165,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M118" s="5" t="n"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -7640,8 +8230,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M119" s="5" t="n"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
     </row>
     <row r="120" ht="18.75" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -7700,8 +8295,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M120" s="5" t="n"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -7760,12 +8360,17 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M121" s="5" t="inlineStr">
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
         <is>
           <t>Clinical study table</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="O121" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023700.png</t>
         </is>
@@ -7828,8 +8433,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M122" s="5" t="n"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -7888,8 +8498,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M123" s="5" t="n"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N123" s="5" t="n"/>
+      <c r="O123" s="5" t="n"/>
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -7948,8 +8563,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M124" s="5" t="n"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -8008,8 +8628,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M125" s="5" t="n"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
     </row>
     <row r="126" ht="18.75" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -8068,8 +8693,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M126" s="5" t="n"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
     </row>
     <row r="127" ht="18.75" customHeight="1">
       <c r="A127" s="3" t="n">
@@ -8128,8 +8758,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M127" s="5" t="n"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -8188,8 +8823,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M128" s="5" t="n"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
     </row>
     <row r="129" ht="18.75" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -8248,8 +8888,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M129" s="5" t="n"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
     </row>
     <row r="130" ht="18.75" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -8308,8 +8953,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M130" s="5" t="n"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -8368,8 +9018,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M131" s="5" t="n"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
     </row>
     <row r="132" ht="18.75" customHeight="1">
       <c r="A132" s="3" t="n">
@@ -8428,8 +9083,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M132" s="5" t="n"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
     </row>
     <row r="133" ht="18.75" customHeight="1">
       <c r="A133" s="3" t="n">
@@ -8488,8 +9148,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M133" s="5" t="n"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
     </row>
     <row r="134" ht="18.75" customHeight="1">
       <c r="A134" s="3" t="n">
@@ -8548,12 +9213,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M134" s="5" t="inlineStr">
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
         <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N134" s="5" t="inlineStr">
+      <c r="O134" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023713.png</t>
         </is>
@@ -8616,12 +9286,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M135" s="5" t="inlineStr">
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
         <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N135" s="5" t="inlineStr">
+      <c r="O135" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023714.png</t>
         </is>
@@ -8684,8 +9359,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M136" s="5" t="n"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
     </row>
     <row r="137" ht="18.75" customHeight="1">
       <c r="A137" s="3" t="n">
@@ -8744,8 +9424,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M137" s="5" t="n"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
     </row>
     <row r="138" ht="18.75" customHeight="1">
       <c r="A138" s="3" t="n">
@@ -8804,8 +9489,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M138" s="5" t="n"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
     </row>
     <row r="139" ht="18.75" customHeight="1">
       <c r="A139" s="3" t="n">
@@ -8864,12 +9554,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="inlineStr">
         <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="O139" s="5" t="inlineStr">
         <is>
           <t>images/2024/ssm2023718.png</t>
         </is>
@@ -8932,8 +9627,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M140" s="5" t="n"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
     </row>
     <row r="141" ht="18.75" customHeight="1">
       <c r="A141" s="3" t="n">
@@ -8992,8 +9692,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M141" s="5" t="n"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N141" s="5" t="n"/>
+      <c r="O141" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
